--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,15 +362,6 @@
     <t>fr-lm-section.subSection</t>
   </si>
   <si>
-    <t>fr-lm-exposure-information.entry</t>
-  </si>
-  <si>
-    <t>Entrées</t>
-  </si>
-  <si>
-    <t>fr-lm-section.entry</t>
-  </si>
-  <si>
     <t>fr-lm-exposure-information.subSection.quantityExposure</t>
   </si>
   <si>
@@ -389,6 +380,15 @@
   </si>
   <si>
     <t>Entrée administration des produits radiopharmaceutiques</t>
+  </si>
+  <si>
+    <t>fr-lm-exposure-information.entry</t>
+  </si>
+  <si>
+    <t>Entrées</t>
+  </si>
+  <si>
+    <t>fr-lm-section.entry</t>
   </si>
 </sst>
 </file>
@@ -1868,13 +1868,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1925,7 +1925,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1956,7 +1956,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2031,7 +2031,7 @@
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2056,7 +2056,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2068,13 +2068,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>121</v>
-      </c>
       <c r="M14" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2125,13 +2125,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>

--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-exposure-information.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
